--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -964,7 +964,7 @@
     <t>0.0001,0.9998,0.0006,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9996,0.1583,0.0001</t>
+    <t>0.0001,0.9996,0.1584,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9998,0.0194,0.0001</t>
@@ -1426,7 +1426,7 @@
     <t>0.4726,0.5900,0.0163,0.0022</t>
   </si>
   <si>
-    <t>0.3753,0.6052,0.0183,0.0013</t>
+    <t>0.3753,0.6052,0.0184,0.0013</t>
   </si>
   <si>
     <t>0.9460,0.0027,0.0378,0.0003</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
   <si>
     <t>Filename</t>
   </si>
@@ -826,16 +826,25 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9523,0.0016,0.0127,0.0027</t>
-  </si>
-  <si>
-    <t>0.0032,0.0060,0.0005,0.9991</t>
-  </si>
-  <si>
-    <t>0.9693,0.0017,0.0014,0.0103</t>
-  </si>
-  <si>
-    <t>0.3492,0.0003,0.0012,0.7249</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9524,0.0016,0.0126,0.0027</t>
+  </si>
+  <si>
+    <t>0.0032,0.0059,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.9694,0.0017,0.0013,0.0102</t>
+  </si>
+  <si>
+    <t>0.3496,0.0003,0.0012,0.7252</t>
   </si>
   <si>
     <t>0.9944,0.0016,0.0009,0.0002</t>
@@ -844,37 +853,37 @@
     <t>0.9842,0.0104,0.0016,0.0007</t>
   </si>
   <si>
-    <t>0.9903,0.0032,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9942,0.0015,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9726,0.0243,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9831,0.0137,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.9917,0.0022,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9913,0.0024,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.7959,0.0140,0.1680,0.0022</t>
-  </si>
-  <si>
-    <t>0.0162,0.0357,0.9612,0.0017</t>
-  </si>
-  <si>
-    <t>0.1024,0.0002,0.9501,0.0001</t>
-  </si>
-  <si>
-    <t>0.0510,0.0032,0.9641,0.0009</t>
-  </si>
-  <si>
-    <t>0.8231,0.0005,0.2148,0.0001</t>
+    <t>0.9904,0.0032,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0014,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9727,0.0243,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9832,0.0137,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9917,0.0021,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9914,0.0024,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.7963,0.0140,0.1674,0.0022</t>
+  </si>
+  <si>
+    <t>0.0162,0.0359,0.9610,0.0017</t>
+  </si>
+  <si>
+    <t>0.1026,0.0002,0.9500,0.0001</t>
+  </si>
+  <si>
+    <t>0.0511,0.0032,0.9641,0.0009</t>
+  </si>
+  <si>
+    <t>0.8241,0.0005,0.2133,0.0001</t>
   </si>
   <si>
     <t>0.0006,0.9990,0.0008,0.0003</t>
@@ -883,7 +892,7 @@
     <t>0.0031,0.9956,0.0009,0.0011</t>
   </si>
   <si>
-    <t>0.0615,0.9696,0.0267,0.0002</t>
+    <t>0.0616,0.9695,0.0265,0.0002</t>
   </si>
   <si>
     <t>0.0053,0.9916,0.0014,0.0035</t>
@@ -892,19 +901,19 @@
     <t>0.0004,0.9995,0.0012,0.0000</t>
   </si>
   <si>
-    <t>0.2347,0.0021,0.8276,0.0011</t>
-  </si>
-  <si>
-    <t>0.0851,0.0050,0.9314,0.0019</t>
+    <t>0.2354,0.0021,0.8271,0.0011</t>
+  </si>
+  <si>
+    <t>0.0853,0.0050,0.9312,0.0019</t>
   </si>
   <si>
     <t>0.0263,0.0001,0.9899,0.0000</t>
   </si>
   <si>
-    <t>0.0187,0.0017,0.9860,0.0007</t>
-  </si>
-  <si>
-    <t>0.0125,0.0009,0.9925,0.0003</t>
+    <t>0.0188,0.0017,0.9860,0.0007</t>
+  </si>
+  <si>
+    <t>0.0125,0.0009,0.9924,0.0003</t>
   </si>
   <si>
     <t>0.0356,0.0002,0.9794,0.0002</t>
@@ -913,109 +922,109 @@
     <t>0.0072,0.0002,0.9932,0.0009</t>
   </si>
   <si>
-    <t>0.6881,0.2356,0.0680,0.0023</t>
-  </si>
-  <si>
-    <t>0.8708,0.1271,0.0151,0.0008</t>
+    <t>0.6886,0.2358,0.0675,0.0023</t>
+  </si>
+  <si>
+    <t>0.8710,0.1271,0.0151,0.0008</t>
   </si>
   <si>
     <t>0.0019,0.0002,0.9986,0.0002</t>
   </si>
   <si>
-    <t>0.0065,0.4610,0.8709,0.0018</t>
-  </si>
-  <si>
-    <t>0.9407,0.0037,0.0291,0.0005</t>
-  </si>
-  <si>
-    <t>0.9155,0.0125,0.0454,0.0004</t>
-  </si>
-  <si>
-    <t>0.2357,0.8257,0.0382,0.0019</t>
-  </si>
-  <si>
-    <t>0.0061,0.9498,0.7738,0.0005</t>
-  </si>
-  <si>
-    <t>0.0025,0.8545,0.9352,0.0007</t>
+    <t>0.0065,0.4622,0.8703,0.0018</t>
+  </si>
+  <si>
+    <t>0.9411,0.0037,0.0289,0.0005</t>
+  </si>
+  <si>
+    <t>0.9156,0.0125,0.0453,0.0004</t>
+  </si>
+  <si>
+    <t>0.2360,0.8257,0.0378,0.0019</t>
+  </si>
+  <si>
+    <t>0.0061,0.9499,0.7730,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.8546,0.9350,0.0007</t>
   </si>
   <si>
     <t>0.0015,0.0005,0.9977,0.0004</t>
   </si>
   <si>
-    <t>0.0116,0.0166,0.9752,0.0025</t>
-  </si>
-  <si>
-    <t>0.1775,0.0002,0.8299,0.0034</t>
-  </si>
-  <si>
-    <t>0.0022,0.2668,0.9833,0.0006</t>
+    <t>0.0117,0.0166,0.9752,0.0025</t>
+  </si>
+  <si>
+    <t>0.1783,0.0002,0.8289,0.0034</t>
+  </si>
+  <si>
+    <t>0.0022,0.2667,0.9833,0.0006</t>
   </si>
   <si>
     <t>0.0009,0.9949,0.0076,0.0049</t>
   </si>
   <si>
-    <t>0.0031,0.0087,0.9936,0.0010</t>
-  </si>
-  <si>
-    <t>0.0052,0.8543,0.0012,0.7111</t>
+    <t>0.0031,0.0086,0.9936,0.0010</t>
+  </si>
+  <si>
+    <t>0.0052,0.8540,0.0011,0.7120</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0006,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9996,0.1584,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0194,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0548,0.9951,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0467,0.9965,0.0003</t>
+    <t>0.0001,0.9996,0.1576,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0193,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0546,0.9951,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0466,0.9965,0.0003</t>
   </si>
   <si>
     <t>0.0139,0.0013,0.9864,0.0018</t>
   </si>
   <si>
-    <t>0.0241,0.0001,0.9911,0.0000</t>
+    <t>0.0242,0.0001,0.9911,0.0000</t>
   </si>
   <si>
     <t>0.0056,0.0004,0.9959,0.0002</t>
   </si>
   <si>
-    <t>0.0348,0.0068,0.9587,0.0020</t>
-  </si>
-  <si>
-    <t>0.9539,0.0173,0.0212,0.0004</t>
-  </si>
-  <si>
-    <t>0.9567,0.0013,0.0300,0.0002</t>
-  </si>
-  <si>
-    <t>0.9807,0.0030,0.0065,0.0009</t>
-  </si>
-  <si>
-    <t>0.4805,0.0008,0.6316,0.0002</t>
-  </si>
-  <si>
-    <t>0.9795,0.0011,0.0114,0.0002</t>
-  </si>
-  <si>
-    <t>0.9837,0.0032,0.0078,0.0004</t>
+    <t>0.0349,0.0068,0.9586,0.0020</t>
+  </si>
+  <si>
+    <t>0.9542,0.0172,0.0210,0.0004</t>
+  </si>
+  <si>
+    <t>0.9569,0.0013,0.0298,0.0002</t>
+  </si>
+  <si>
+    <t>0.9808,0.0029,0.0064,0.0009</t>
+  </si>
+  <si>
+    <t>0.4832,0.0008,0.6287,0.0002</t>
+  </si>
+  <si>
+    <t>0.9796,0.0011,0.0113,0.0002</t>
+  </si>
+  <si>
+    <t>0.9838,0.0032,0.0077,0.0004</t>
   </si>
   <si>
     <t>0.9927,0.0010,0.0029,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9975,0.9442,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0273,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0031,0.9961,0.0006</t>
+    <t>0.0001,0.9975,0.9440,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0272,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.0031,0.9961,0.0007</t>
   </si>
   <si>
     <t>0.0004,0.9741,0.9717,0.0001</t>
@@ -1024,16 +1033,16 @@
     <t>0.0001,0.0000,0.9997,0.0001</t>
   </si>
   <si>
-    <t>0.0012,0.9989,0.0018,0.0000</t>
+    <t>0.0012,0.9989,0.0017,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9719,0.0009,0.0245,0.0001</t>
-  </si>
-  <si>
-    <t>0.1732,0.0450,0.7940,0.0072</t>
+    <t>0.9720,0.0009,0.0244,0.0001</t>
+  </si>
+  <si>
+    <t>0.1739,0.0451,0.7930,0.0072</t>
   </si>
   <si>
     <t>0.0078,0.0033,0.9928,0.0011</t>
@@ -1042,16 +1051,16 @@
     <t>0.0005,0.9753,0.9687,0.0002</t>
   </si>
   <si>
-    <t>0.0002,0.9545,0.9919,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0457,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9900,0.8911,0.0003</t>
-  </si>
-  <si>
-    <t>0.0198,0.0066,0.0023,0.9798</t>
+    <t>0.0002,0.9544,0.9919,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0455,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9900,0.8908,0.0003</t>
+  </si>
+  <si>
+    <t>0.0197,0.0066,0.0022,0.9798</t>
   </si>
   <si>
     <t>0.0004,0.0004,0.0001,1.0000</t>
@@ -1063,88 +1072,88 @@
     <t>0.0032,0.0008,0.0017,0.9993</t>
   </si>
   <si>
-    <t>0.0350,0.0032,0.0022,0.9796</t>
+    <t>0.0349,0.0032,0.0022,0.9796</t>
   </si>
   <si>
     <t>0.0002,0.0013,0.0015,0.9999</t>
   </si>
   <si>
-    <t>0.0001,0.9958,0.9668,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.4685,0.9947,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9329,0.6964,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.9289,0.9851,0.0002</t>
+    <t>0.0001,0.9958,0.9667,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.4675,0.9947,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9328,0.6956,0.0013</t>
+  </si>
+  <si>
+    <t>0.0005,0.9288,0.9850,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.9928,0.9843,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.9921,0.8898,0.0001</t>
+    <t>0.0004,0.9921,0.8892,0.0001</t>
   </si>
   <si>
     <t>0.9944,0.0034,0.0004,0.0002</t>
   </si>
   <si>
-    <t>0.9677,0.0306,0.0050,0.0008</t>
+    <t>0.9679,0.0304,0.0049,0.0008</t>
   </si>
   <si>
     <t>0.9558,0.0397,0.0006,0.0002</t>
   </si>
   <si>
-    <t>0.9863,0.0138,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.9860,0.0079,0.0035,0.0003</t>
+    <t>0.9864,0.0137,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9861,0.0079,0.0035,0.0003</t>
   </si>
   <si>
     <t>0.9943,0.0019,0.0005,0.0003</t>
   </si>
   <si>
-    <t>0.9847,0.0023,0.0067,0.0004</t>
+    <t>0.9848,0.0022,0.0066,0.0004</t>
   </si>
   <si>
     <t>0.9937,0.0014,0.0010,0.0004</t>
   </si>
   <si>
-    <t>0.9934,0.0015,0.0012,0.0004</t>
+    <t>0.9935,0.0015,0.0012,0.0004</t>
   </si>
   <si>
     <t>0.9836,0.0097,0.0016,0.0002</t>
   </si>
   <si>
-    <t>0.9941,0.0029,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9970,0.0010,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9812,0.0051,0.0032,0.0015</t>
+    <t>0.9942,0.0029,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9813,0.0051,0.0031,0.0015</t>
   </si>
   <si>
     <t>0.9963,0.0015,0.0002,0.0001</t>
   </si>
   <si>
-    <t>0.9945,0.0022,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9912,0.0031,0.0017,0.0003</t>
+    <t>0.9946,0.0022,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9913,0.0031,0.0017,0.0003</t>
   </si>
   <si>
     <t>0.0008,0.0001,0.9993,0.0001</t>
   </si>
   <si>
-    <t>0.0825,0.0007,0.9543,0.0004</t>
-  </si>
-  <si>
-    <t>0.9459,0.0003,0.0909,0.0000</t>
-  </si>
-  <si>
-    <t>0.0588,0.0008,0.9626,0.0004</t>
+    <t>0.0826,0.0007,0.9542,0.0004</t>
+  </si>
+  <si>
+    <t>0.9461,0.0003,0.0905,0.0000</t>
+  </si>
+  <si>
+    <t>0.0589,0.0008,0.9626,0.0004</t>
   </si>
   <si>
     <t>0.0003,0.9995,0.0001,0.0001</t>
@@ -1153,31 +1162,31 @@
     <t>0.0001,0.9998,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6357,0.5211,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.1058,0.9112,0.0240,0.0019</t>
+    <t>0.6361,0.5206,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.1061,0.9110,0.0237,0.0019</t>
   </si>
   <si>
     <t>0.0004,0.9995,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6736,0.3813,0.0365,0.0023</t>
-  </si>
-  <si>
-    <t>0.1273,0.0114,0.8804,0.0034</t>
-  </si>
-  <si>
-    <t>0.0365,0.0018,0.9700,0.0013</t>
-  </si>
-  <si>
-    <t>0.4429,0.0121,0.5519,0.0039</t>
-  </si>
-  <si>
-    <t>0.1196,0.0097,0.8920,0.0043</t>
-  </si>
-  <si>
-    <t>0.0017,0.4710,0.8121,0.0279</t>
+    <t>0.6749,0.3807,0.0362,0.0023</t>
+  </si>
+  <si>
+    <t>0.1281,0.0114,0.8795,0.0035</t>
+  </si>
+  <si>
+    <t>0.0366,0.0018,0.9700,0.0013</t>
+  </si>
+  <si>
+    <t>0.4442,0.0121,0.5503,0.0039</t>
+  </si>
+  <si>
+    <t>0.1201,0.0097,0.8915,0.0044</t>
+  </si>
+  <si>
+    <t>0.0017,0.4711,0.8112,0.0280</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0081,0.0001</t>
@@ -1189,46 +1198,46 @@
     <t>0.0002,0.9990,0.0004,0.0024</t>
   </si>
   <si>
-    <t>0.0001,0.9992,0.0781,0.0005</t>
-  </si>
-  <si>
-    <t>0.0033,0.9916,0.1992,0.0006</t>
-  </si>
-  <si>
-    <t>0.6488,0.2775,0.0640,0.0010</t>
-  </si>
-  <si>
-    <t>0.3920,0.5904,0.0755,0.0053</t>
-  </si>
-  <si>
-    <t>0.9940,0.0003,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9786,0.0141,0.0007,0.0007</t>
+    <t>0.0001,0.9992,0.0778,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.9916,0.1980,0.0006</t>
+  </si>
+  <si>
+    <t>0.6499,0.2774,0.0635,0.0010</t>
+  </si>
+  <si>
+    <t>0.3929,0.5901,0.0749,0.0053</t>
+  </si>
+  <si>
+    <t>0.9940,0.0003,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9786,0.0141,0.0007,0.0006</t>
   </si>
   <si>
     <t>0.9886,0.0045,0.0017,0.0005</t>
   </si>
   <si>
-    <t>0.9841,0.0019,0.0067,0.0003</t>
+    <t>0.9842,0.0019,0.0066,0.0003</t>
   </si>
   <si>
     <t>0.9967,0.0013,0.0004,0.0001</t>
   </si>
   <si>
-    <t>0.9713,0.0006,0.0126,0.0003</t>
+    <t>0.9715,0.0006,0.0125,0.0003</t>
   </si>
   <si>
     <t>0.9895,0.0016,0.0029,0.0004</t>
   </si>
   <si>
-    <t>0.9936,0.0010,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.0023,0.9162,0.9353,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.4996,0.9979,0.0000</t>
+    <t>0.9937,0.0010,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.9161,0.9351,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.4990,0.9979,0.0000</t>
   </si>
   <si>
     <t>0.0002,0.0027,0.9989,0.0009</t>
@@ -1237,19 +1246,19 @@
     <t>0.0044,0.0177,0.9947,0.0002</t>
   </si>
   <si>
-    <t>0.9508,0.0023,0.0441,0.0002</t>
-  </si>
-  <si>
-    <t>0.5356,0.1958,0.1025,0.0074</t>
-  </si>
-  <si>
-    <t>0.0965,0.0001,0.9383,0.0006</t>
-  </si>
-  <si>
-    <t>0.7839,0.0108,0.1839,0.0020</t>
-  </si>
-  <si>
-    <t>0.0188,0.0002,0.0022,0.9962</t>
+    <t>0.9510,0.0023,0.0439,0.0002</t>
+  </si>
+  <si>
+    <t>0.5351,0.1966,0.1020,0.0074</t>
+  </si>
+  <si>
+    <t>0.0966,0.0001,0.9383,0.0006</t>
+  </si>
+  <si>
+    <t>0.7845,0.0108,0.1832,0.0020</t>
+  </si>
+  <si>
+    <t>0.0188,0.0002,0.0021,0.9962</t>
   </si>
   <si>
     <t>0.0000,0.0005,0.0001,1.0000</t>
@@ -1264,13 +1273,13 @@
     <t>0.0001,0.9950,0.9717,0.0000</t>
   </si>
   <si>
-    <t>0.9790,0.0007,0.0096,0.0004</t>
-  </si>
-  <si>
-    <t>0.0127,0.9782,0.0067,0.0092</t>
-  </si>
-  <si>
-    <t>0.9939,0.0004,0.0023,0.0001</t>
+    <t>0.9791,0.0007,0.0095,0.0004</t>
+  </si>
+  <si>
+    <t>0.0127,0.9782,0.0066,0.0092</t>
+  </si>
+  <si>
+    <t>0.9939,0.0004,0.0022,0.0001</t>
   </si>
   <si>
     <t>0.0303,0.9703,0.0066,0.0020</t>
@@ -1279,55 +1288,55 @@
     <t>0.9958,0.0003,0.0006,0.0003</t>
   </si>
   <si>
-    <t>0.5528,0.0000,0.5136,0.0000</t>
-  </si>
-  <si>
-    <t>0.7716,0.0000,0.2539,0.0001</t>
+    <t>0.5543,0.0000,0.5118,0.0000</t>
+  </si>
+  <si>
+    <t>0.7723,0.0000,0.2529,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9677,0.0000,0.0144,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0013,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.8598,0.0615,0.0252,0.0006</t>
-  </si>
-  <si>
-    <t>0.9866,0.0010,0.0063,0.0002</t>
-  </si>
-  <si>
-    <t>0.8959,0.0332,0.0447,0.0022</t>
-  </si>
-  <si>
-    <t>0.0930,0.8689,0.0237,0.0229</t>
-  </si>
-  <si>
-    <t>0.9188,0.0315,0.0305,0.0008</t>
-  </si>
-  <si>
-    <t>0.9408,0.0112,0.0343,0.0008</t>
-  </si>
-  <si>
-    <t>0.9910,0.0050,0.0011,0.0002</t>
+    <t>0.9679,0.0000,0.0143,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0013,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.8600,0.0616,0.0250,0.0006</t>
+  </si>
+  <si>
+    <t>0.9866,0.0010,0.0062,0.0002</t>
+  </si>
+  <si>
+    <t>0.8963,0.0332,0.0444,0.0022</t>
+  </si>
+  <si>
+    <t>0.0930,0.8689,0.0235,0.0229</t>
+  </si>
+  <si>
+    <t>0.9191,0.0315,0.0303,0.0008</t>
+  </si>
+  <si>
+    <t>0.9409,0.0112,0.0342,0.0008</t>
+  </si>
+  <si>
+    <t>0.9911,0.0050,0.0011,0.0002</t>
   </si>
   <si>
     <t>0.9951,0.0017,0.0004,0.0003</t>
   </si>
   <si>
-    <t>0.9857,0.0040,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.9870,0.0009,0.0043,0.0003</t>
+    <t>0.9857,0.0040,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.9871,0.0009,0.0043,0.0003</t>
   </si>
   <si>
     <t>0.9944,0.0035,0.0008,0.0000</t>
   </si>
   <si>
-    <t>0.9881,0.0068,0.0017,0.0003</t>
+    <t>0.9881,0.0067,0.0017,0.0003</t>
   </si>
   <si>
     <t>0.9904,0.0033,0.0017,0.0002</t>
@@ -1336,46 +1345,46 @@
     <t>0.9930,0.0016,0.0013,0.0002</t>
   </si>
   <si>
-    <t>0.7738,0.2436,0.0131,0.0082</t>
-  </si>
-  <si>
-    <t>0.4819,0.5931,0.0123,0.0061</t>
-  </si>
-  <si>
-    <t>0.8915,0.1104,0.0051,0.0014</t>
-  </si>
-  <si>
-    <t>0.7624,0.0056,0.2329,0.0004</t>
-  </si>
-  <si>
-    <t>0.9788,0.0068,0.0074,0.0005</t>
-  </si>
-  <si>
-    <t>0.9340,0.0150,0.0310,0.0007</t>
-  </si>
-  <si>
-    <t>0.9786,0.0043,0.0087,0.0003</t>
-  </si>
-  <si>
-    <t>0.8899,0.0705,0.0392,0.0050</t>
+    <t>0.7740,0.2432,0.0130,0.0081</t>
+  </si>
+  <si>
+    <t>0.4821,0.5927,0.0122,0.0061</t>
+  </si>
+  <si>
+    <t>0.8916,0.1103,0.0050,0.0014</t>
+  </si>
+  <si>
+    <t>0.7644,0.0056,0.2305,0.0004</t>
+  </si>
+  <si>
+    <t>0.9789,0.0067,0.0073,0.0005</t>
+  </si>
+  <si>
+    <t>0.9344,0.0149,0.0307,0.0007</t>
+  </si>
+  <si>
+    <t>0.9787,0.0043,0.0086,0.0003</t>
+  </si>
+  <si>
+    <t>0.8904,0.0703,0.0389,0.0050</t>
   </si>
   <si>
     <t>0.0034,0.0025,0.9979,0.0001</t>
   </si>
   <si>
-    <t>0.9469,0.0119,0.0280,0.0003</t>
+    <t>0.9472,0.0119,0.0277,0.0003</t>
   </si>
   <si>
     <t>0.0006,0.0001,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0750,0.9888,0.0034</t>
-  </si>
-  <si>
-    <t>0.0077,0.0013,0.9936,0.0009</t>
-  </si>
-  <si>
-    <t>0.0047,0.4947,0.9235,0.0007</t>
+    <t>0.0006,0.0748,0.9887,0.0034</t>
+  </si>
+  <si>
+    <t>0.0077,0.0012,0.9936,0.0009</t>
+  </si>
+  <si>
+    <t>0.0047,0.4952,0.9232,0.0007</t>
   </si>
   <si>
     <t>0.0031,0.0008,0.9980,0.0001</t>
@@ -1387,106 +1396,106 @@
     <t>0.0112,0.0003,0.9934,0.0002</t>
   </si>
   <si>
-    <t>0.0833,0.0016,0.9396,0.0014</t>
-  </si>
-  <si>
-    <t>0.1120,0.0024,0.9029,0.0017</t>
-  </si>
-  <si>
-    <t>0.6817,0.0563,0.2193,0.0066</t>
-  </si>
-  <si>
-    <t>0.0291,0.0074,0.9687,0.0032</t>
-  </si>
-  <si>
-    <t>0.0120,0.0407,0.9709,0.0007</t>
-  </si>
-  <si>
-    <t>0.0609,0.0024,0.9450,0.0023</t>
-  </si>
-  <si>
-    <t>0.1511,0.0039,0.8629,0.0034</t>
-  </si>
-  <si>
-    <t>0.4660,0.0091,0.5610,0.0017</t>
-  </si>
-  <si>
-    <t>0.3274,0.8032,0.0025,0.0001</t>
+    <t>0.0835,0.0016,0.9395,0.0014</t>
+  </si>
+  <si>
+    <t>0.1123,0.0024,0.9025,0.0017</t>
+  </si>
+  <si>
+    <t>0.6822,0.0564,0.2185,0.0066</t>
+  </si>
+  <si>
+    <t>0.0291,0.0074,0.9686,0.0033</t>
+  </si>
+  <si>
+    <t>0.0121,0.0408,0.9708,0.0007</t>
+  </si>
+  <si>
+    <t>0.0610,0.0024,0.9450,0.0023</t>
+  </si>
+  <si>
+    <t>0.1515,0.0039,0.8624,0.0034</t>
+  </si>
+  <si>
+    <t>0.4669,0.0091,0.5597,0.0017</t>
+  </si>
+  <si>
+    <t>0.3279,0.8029,0.0024,0.0001</t>
   </si>
   <si>
     <t>0.0025,0.9970,0.0014,0.0003</t>
   </si>
   <si>
-    <t>0.0702,0.9534,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.9620,0.0291,0.0082,0.0005</t>
-  </si>
-  <si>
-    <t>0.4726,0.5900,0.0163,0.0022</t>
-  </si>
-  <si>
-    <t>0.3753,0.6052,0.0184,0.0013</t>
-  </si>
-  <si>
-    <t>0.9460,0.0027,0.0378,0.0003</t>
-  </si>
-  <si>
-    <t>0.5462,0.0192,0.3975,0.0090</t>
-  </si>
-  <si>
-    <t>0.1611,0.0004,0.8764,0.0021</t>
-  </si>
-  <si>
-    <t>0.6946,0.0048,0.2289,0.0027</t>
+    <t>0.0704,0.9534,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.9622,0.0290,0.0081,0.0005</t>
+  </si>
+  <si>
+    <t>0.4742,0.5889,0.0161,0.0022</t>
+  </si>
+  <si>
+    <t>0.3753,0.6059,0.0182,0.0013</t>
+  </si>
+  <si>
+    <t>0.9462,0.0027,0.0375,0.0003</t>
+  </si>
+  <si>
+    <t>0.5469,0.0192,0.3963,0.0090</t>
+  </si>
+  <si>
+    <t>0.1613,0.0004,0.8762,0.0021</t>
+  </si>
+  <si>
+    <t>0.6956,0.0048,0.2277,0.0027</t>
   </si>
   <si>
     <t>0.0051,0.0004,0.9953,0.0008</t>
   </si>
   <si>
-    <t>0.0297,0.0034,0.9797,0.0009</t>
-  </si>
-  <si>
-    <t>0.0340,0.0133,0.9670,0.0004</t>
+    <t>0.0299,0.0034,0.9796,0.0009</t>
+  </si>
+  <si>
+    <t>0.0341,0.0133,0.9669,0.0004</t>
   </si>
   <si>
     <t>0.0060,0.0025,0.9934,0.0004</t>
   </si>
   <si>
-    <t>0.0681,0.0025,0.9442,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0007,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9671,0.0337,0.0061,0.0009</t>
-  </si>
-  <si>
-    <t>0.9606,0.0207,0.0085,0.0027</t>
+    <t>0.0684,0.0025,0.9438,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0007,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9673,0.0336,0.0061,0.0009</t>
+  </si>
+  <si>
+    <t>0.9607,0.0206,0.0085,0.0027</t>
   </si>
   <si>
     <t>0.9847,0.0098,0.0008,0.0005</t>
   </si>
   <si>
-    <t>0.9262,0.0523,0.0191,0.0040</t>
-  </si>
-  <si>
-    <t>0.9594,0.0293,0.0073,0.0031</t>
-  </si>
-  <si>
-    <t>0.9804,0.0083,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.9950,0.0008,0.0013,0.0001</t>
+    <t>0.9266,0.0520,0.0189,0.0040</t>
+  </si>
+  <si>
+    <t>0.9596,0.0292,0.0073,0.0031</t>
+  </si>
+  <si>
+    <t>0.9804,0.0082,0.0041,0.0006</t>
+  </si>
+  <si>
+    <t>0.9951,0.0008,0.0013,0.0001</t>
   </si>
   <si>
     <t>0.0107,0.0005,0.9936,0.0002</t>
   </si>
   <si>
-    <t>0.0728,0.0114,0.9346,0.0023</t>
-  </si>
-  <si>
-    <t>0.4728,0.0075,0.4432,0.0113</t>
+    <t>0.0734,0.0115,0.9340,0.0023</t>
+  </si>
+  <si>
+    <t>0.4743,0.0075,0.4412,0.0113</t>
   </si>
   <si>
     <t>0.0004,0.0001,0.9997,0.0000</t>
@@ -1495,7 +1504,7 @@
     <t>0.0002,0.0013,0.9995,0.0002</t>
   </si>
   <si>
-    <t>0.0073,0.0128,0.9858,0.0009</t>
+    <t>0.0074,0.0128,0.9857,0.0009</t>
   </si>
   <si>
     <t>0.0140,0.0057,0.9853,0.0011</t>
@@ -1504,43 +1513,43 @@
     <t>0.0028,0.0017,0.9967,0.0004</t>
   </si>
   <si>
-    <t>0.0312,0.0145,0.9531,0.0065</t>
-  </si>
-  <si>
-    <t>0.7206,0.0008,0.3039,0.0014</t>
-  </si>
-  <si>
-    <t>0.3932,0.0005,0.5351,0.0095</t>
-  </si>
-  <si>
-    <t>0.9365,0.0046,0.0446,0.0003</t>
-  </si>
-  <si>
-    <t>0.9925,0.0034,0.0011,0.0002</t>
+    <t>0.0312,0.0145,0.9530,0.0066</t>
+  </si>
+  <si>
+    <t>0.7212,0.0008,0.3029,0.0014</t>
+  </si>
+  <si>
+    <t>0.3944,0.0005,0.5334,0.0096</t>
+  </si>
+  <si>
+    <t>0.9368,0.0046,0.0442,0.0003</t>
+  </si>
+  <si>
+    <t>0.9926,0.0034,0.0011,0.0002</t>
   </si>
   <si>
     <t>0.9903,0.0070,0.0004,0.0003</t>
   </si>
   <si>
-    <t>0.9904,0.0069,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9358,0.0516,0.0129,0.0018</t>
+    <t>0.9905,0.0068,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9361,0.0514,0.0128,0.0018</t>
   </si>
   <si>
     <t>0.9944,0.0007,0.0017,0.0001</t>
   </si>
   <si>
-    <t>0.9817,0.0155,0.0027,0.0006</t>
+    <t>0.9818,0.0154,0.0027,0.0006</t>
   </si>
   <si>
     <t>0.9894,0.0073,0.0016,0.0008</t>
   </si>
   <si>
-    <t>0.9883,0.0027,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.0039,0.1464,0.9203,0.0018</t>
+    <t>0.9884,0.0027,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.0039,0.1466,0.9201,0.0018</t>
   </si>
   <si>
     <t>0.0016,0.0075,0.9983,0.0001</t>
@@ -1549,37 +1558,37 @@
     <t>0.0015,0.0020,0.9986,0.0001</t>
   </si>
   <si>
-    <t>0.0239,0.0141,0.9550,0.0018</t>
+    <t>0.0239,0.0142,0.9549,0.0018</t>
   </si>
   <si>
     <t>0.0087,0.0002,0.9955,0.0001</t>
   </si>
   <si>
-    <t>0.1381,0.0126,0.1751,0.3130</t>
-  </si>
-  <si>
-    <t>0.0929,0.0079,0.9096,0.0058</t>
+    <t>0.1381,0.0126,0.1735,0.3145</t>
+  </si>
+  <si>
+    <t>0.0932,0.0079,0.9092,0.0058</t>
   </si>
   <si>
     <t>0.0014,0.0000,0.9971,0.0011</t>
   </si>
   <si>
-    <t>0.9732,0.0003,0.0053,0.0019</t>
+    <t>0.9733,0.0003,0.0052,0.0019</t>
   </si>
   <si>
     <t>0.0008,0.0104,0.0002,0.9998</t>
   </si>
   <si>
-    <t>0.0557,0.0006,0.0058,0.9861</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0449,0.9994</t>
+    <t>0.0556,0.0006,0.0057,0.9862</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0447,0.9994</t>
   </si>
   <si>
     <t>0.0002,0.0009,0.0011,0.9999</t>
   </si>
   <si>
-    <t>0.7805,0.0068,0.0155,0.1442</t>
+    <t>0.7807,0.0068,0.0153,0.1441</t>
   </si>
 </sst>
 </file>
@@ -1965,7 +1974,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1979,7 +1988,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1993,7 +2002,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2007,7 +2016,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2021,7 +2030,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2035,7 +2044,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2049,7 +2058,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2063,7 +2072,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2077,7 +2086,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2091,7 +2100,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2105,7 +2114,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2119,7 +2128,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2133,7 +2142,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2147,7 +2156,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2161,7 +2170,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2175,7 +2184,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2189,7 +2198,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2203,7 +2212,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2217,7 +2226,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2231,7 +2240,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2245,7 +2254,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2259,7 +2268,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2273,7 +2282,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2287,7 +2296,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2301,7 +2310,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2315,7 +2324,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2329,7 +2338,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2343,7 +2352,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2357,7 +2366,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2371,7 +2380,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2385,7 +2394,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2399,7 +2408,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2413,7 +2422,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2427,7 +2436,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2441,7 +2450,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2455,7 +2464,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2469,7 +2478,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2483,7 +2492,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2497,7 +2506,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2511,7 +2520,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2525,7 +2534,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2539,7 +2548,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2553,7 +2562,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2567,7 +2576,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2581,7 +2590,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2595,7 +2604,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2609,7 +2618,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2623,7 +2632,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2637,7 +2646,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2651,7 +2660,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2665,7 +2674,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2679,7 +2688,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2693,7 +2702,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2707,7 +2716,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2721,7 +2730,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2735,7 +2744,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2749,7 +2758,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2763,7 +2772,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2777,7 +2786,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2791,7 +2800,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2805,7 +2814,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2819,7 +2828,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2833,7 +2842,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2847,7 +2856,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2861,7 +2870,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2875,7 +2884,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2889,7 +2898,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2903,7 +2912,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2917,7 +2926,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2931,7 +2940,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2945,7 +2954,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2959,7 +2968,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2973,7 +2982,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2987,7 +2996,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3001,7 +3010,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3015,7 +3024,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3029,7 +3038,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3043,7 +3052,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3057,7 +3066,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3071,7 +3080,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3085,7 +3094,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3099,7 +3108,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3113,7 +3122,7 @@
         <v>266</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3127,7 +3136,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3141,7 +3150,7 @@
         <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3155,7 +3164,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3169,7 +3178,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3183,7 +3192,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3197,7 +3206,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3211,7 +3220,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3225,7 +3234,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3239,7 +3248,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3253,7 +3262,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3267,7 +3276,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3281,7 +3290,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3295,7 +3304,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3309,7 +3318,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3323,7 +3332,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3337,7 +3346,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3351,7 +3360,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3365,7 +3374,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3379,7 +3388,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3393,7 +3402,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3407,7 +3416,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3421,7 +3430,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3435,7 +3444,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3449,7 +3458,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3463,7 +3472,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3477,7 +3486,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,10 +3497,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3505,7 +3514,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3519,7 +3528,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3533,7 +3542,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3547,7 +3556,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3561,7 +3570,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3575,7 +3584,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3589,7 +3598,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3603,7 +3612,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3617,7 +3626,7 @@
         <v>266</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3631,7 +3640,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3645,7 +3654,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3659,7 +3668,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3673,7 +3682,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3687,7 +3696,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3701,7 +3710,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3715,7 +3724,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3729,7 +3738,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3743,7 +3752,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3757,7 +3766,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3771,7 +3780,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3785,7 +3794,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3799,7 +3808,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3813,7 +3822,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3827,7 +3836,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3841,7 +3850,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3855,7 +3864,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3869,7 +3878,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3883,7 +3892,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3897,7 +3906,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3911,7 +3920,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3925,7 +3934,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3939,7 +3948,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3953,7 +3962,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3967,7 +3976,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3981,7 +3990,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3995,7 +4004,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4009,7 +4018,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4023,7 +4032,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4037,7 +4046,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4051,7 +4060,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4065,7 +4074,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4079,7 +4088,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,10 +4099,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4107,7 +4116,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4121,7 +4130,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4135,7 +4144,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4149,7 +4158,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4163,7 +4172,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4177,7 +4186,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4191,7 +4200,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4205,7 +4214,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4219,7 +4228,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4233,7 +4242,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4247,7 +4256,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4261,7 +4270,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4275,7 +4284,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4289,7 +4298,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4303,7 +4312,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4317,7 +4326,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4331,7 +4340,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4345,7 +4354,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4359,7 +4368,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4373,7 +4382,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4387,7 +4396,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4401,7 +4410,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4415,7 +4424,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4429,7 +4438,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4443,7 +4452,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4457,7 +4466,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4471,7 +4480,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4485,7 +4494,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4499,7 +4508,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4513,7 +4522,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4527,7 +4536,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4541,7 +4550,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4555,7 +4564,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4569,7 +4578,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4583,7 +4592,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4597,7 +4606,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4611,7 +4620,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4625,7 +4634,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4639,7 +4648,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4653,7 +4662,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4667,7 +4676,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4681,7 +4690,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4695,7 +4704,7 @@
         <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4709,7 +4718,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4723,7 +4732,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4737,7 +4746,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4751,7 +4760,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4765,7 +4774,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4779,7 +4788,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4793,7 +4802,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4807,7 +4816,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4821,7 +4830,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4835,7 +4844,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4849,7 +4858,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4863,7 +4872,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4877,7 +4886,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4891,7 +4900,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4905,7 +4914,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4919,7 +4928,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4933,7 +4942,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4947,7 +4956,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4961,7 +4970,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4975,7 +4984,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4989,7 +4998,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5003,7 +5012,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5017,7 +5026,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5031,7 +5040,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5045,7 +5054,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,10 +5065,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5073,7 +5082,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5087,7 +5096,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5101,7 +5110,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5115,7 +5124,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5129,7 +5138,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5143,7 +5152,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5157,7 +5166,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5171,7 +5180,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5185,7 +5194,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5199,7 +5208,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5213,7 +5222,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5227,7 +5236,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5241,7 +5250,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5255,7 +5264,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5269,7 +5278,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5283,7 +5292,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5297,7 +5306,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5311,7 +5320,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5325,7 +5334,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5339,7 +5348,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5353,7 +5362,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5367,7 +5376,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5381,7 +5390,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5395,7 +5404,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5406,10 +5415,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D248" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5423,7 +5432,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5437,7 +5446,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5451,7 +5460,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5465,7 +5474,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5479,7 +5488,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5493,7 +5502,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5507,7 +5516,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5521,7 +5530,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
